--- a/AAII_Financials/Quarterly/MKZR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MKZR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>MKZR</t>
   </si>
@@ -745,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5400</v>
+        <v>5900</v>
       </c>
       <c r="E8" s="3">
         <v>4500</v>
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2700</v>
+        <v>3200</v>
       </c>
       <c r="E10" s="3">
         <v>1400</v>
@@ -1208,7 +1208,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E18" s="3">
         <v>-2100</v>
@@ -1281,8 +1281,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-500</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1917,8 +1917,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>500</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -3067,7 +3067,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="E58" s="3">
         <v>11000</v>
@@ -3120,7 +3120,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="E59" s="3">
         <v>1600</v>
@@ -3173,7 +3173,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5400</v>
+        <v>27800</v>
       </c>
       <c r="E60" s="3">
         <v>15700</v>
@@ -3226,7 +3226,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>145700</v>
+        <v>124300</v>
       </c>
       <c r="E61" s="3">
         <v>133700</v>
@@ -3279,7 +3279,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
         <v>800</v>
